--- a/EQM_por_epoca.xlsx
+++ b/EQM_por_epoca.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B337"/>
+  <dimension ref="A1:B240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -466,7 +466,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.59954026</v>
+        <v>0.60628061</v>
       </c>
     </row>
     <row r="3">
@@ -474,7 +474,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.56478392</v>
+        <v>0.55815754</v>
       </c>
     </row>
     <row r="4">
@@ -482,7 +482,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.53781823</v>
+        <v>0.52431991</v>
       </c>
     </row>
     <row r="5">
@@ -490,7 +490,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.51481269</v>
+        <v>0.49693052</v>
       </c>
     </row>
     <row r="6">
@@ -498,7 +498,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.4941385</v>
+        <v>0.47295455</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0.47508219</v>
+        <v>0.45118258</v>
       </c>
     </row>
     <row r="8">
@@ -514,7 +514,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>0.45731023</v>
+        <v>0.4310977</v>
       </c>
     </row>
     <row r="9">
@@ -522,7 +522,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>0.44064706</v>
+        <v>0.41244637</v>
       </c>
     </row>
     <row r="10">
@@ -530,7 +530,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>0.42498358</v>
+        <v>0.39507668</v>
       </c>
     </row>
     <row r="11">
@@ -538,7 +538,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.41023975</v>
+        <v>0.378878</v>
       </c>
     </row>
     <row r="12">
@@ -546,7 +546,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>0.39634935</v>
+        <v>0.36375852</v>
       </c>
     </row>
     <row r="13">
@@ -554,7 +554,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>0.3832538</v>
+        <v>0.34963695</v>
       </c>
     </row>
     <row r="14">
@@ -562,7 +562,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>0.37089973</v>
+        <v>0.33643941</v>
       </c>
     </row>
     <row r="15">
@@ -570,7 +570,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>0.35923786</v>
+        <v>0.32409807</v>
       </c>
     </row>
     <row r="16">
@@ -578,7 +578,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>0.34822252</v>
+        <v>0.31255048</v>
       </c>
     </row>
     <row r="17">
@@ -586,7 +586,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>0.33781129</v>
+        <v>0.30173915</v>
       </c>
     </row>
     <row r="18">
@@ -594,7 +594,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>0.32796483</v>
+        <v>0.29161107</v>
       </c>
     </row>
     <row r="19">
@@ -602,7 +602,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>0.31864661</v>
+        <v>0.28211747</v>
       </c>
     </row>
     <row r="20">
@@ -610,7 +610,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>0.30982273</v>
+        <v>0.27321336</v>
       </c>
     </row>
     <row r="21">
@@ -618,7 +618,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>0.30146175</v>
+        <v>0.26485734</v>
       </c>
     </row>
     <row r="22">
@@ -626,7 +626,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>0.29353449</v>
+        <v>0.25701119</v>
       </c>
     </row>
     <row r="23">
@@ -634,7 +634,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>0.28601384</v>
+        <v>0.24963972</v>
       </c>
     </row>
     <row r="24">
@@ -642,7 +642,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>0.27887466</v>
+        <v>0.2427104</v>
       </c>
     </row>
     <row r="25">
@@ -650,7 +650,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>0.27209357</v>
+        <v>0.23619324</v>
       </c>
     </row>
     <row r="26">
@@ -658,7 +658,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>0.26564886</v>
+        <v>0.23006053</v>
       </c>
     </row>
     <row r="27">
@@ -666,7 +666,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>0.25952034</v>
+        <v>0.22428662</v>
       </c>
     </row>
     <row r="28">
@@ -674,7 +674,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>0.25368924</v>
+        <v>0.21884784</v>
       </c>
     </row>
     <row r="29">
@@ -682,7 +682,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>0.24813807</v>
+        <v>0.21372225</v>
       </c>
     </row>
     <row r="30">
@@ -690,7 +690,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>0.24285056</v>
+        <v>0.20888953</v>
       </c>
     </row>
     <row r="31">
@@ -698,7 +698,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>0.23781156</v>
+        <v>0.20433086</v>
       </c>
     </row>
     <row r="32">
@@ -706,7 +706,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>0.23300693</v>
+        <v>0.2000288</v>
       </c>
     </row>
     <row r="33">
@@ -714,7 +714,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>0.22842349</v>
+        <v>0.19596713</v>
       </c>
     </row>
     <row r="34">
@@ -722,7 +722,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>0.22404893</v>
+        <v>0.19213083</v>
       </c>
     </row>
     <row r="35">
@@ -730,7 +730,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>0.21987177</v>
+        <v>0.18850592</v>
       </c>
     </row>
     <row r="36">
@@ -738,7 +738,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>0.21588127</v>
+        <v>0.1850794</v>
       </c>
     </row>
     <row r="37">
@@ -746,7 +746,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>0.2120674</v>
+        <v>0.1818392</v>
       </c>
     </row>
     <row r="38">
@@ -754,7 +754,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>0.20842076</v>
+        <v>0.17877406</v>
       </c>
     </row>
     <row r="39">
@@ -762,7 +762,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>0.20493257</v>
+        <v>0.17587349</v>
       </c>
     </row>
     <row r="40">
@@ -770,7 +770,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>0.20159459</v>
+        <v>0.17312772</v>
       </c>
     </row>
     <row r="41">
@@ -778,7 +778,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>0.19839909</v>
+        <v>0.17052763</v>
       </c>
     </row>
     <row r="42">
@@ -786,7 +786,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>0.19533885</v>
+        <v>0.16806472</v>
       </c>
     </row>
     <row r="43">
@@ -794,7 +794,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>0.19240706</v>
+        <v>0.16573104</v>
       </c>
     </row>
     <row r="44">
@@ -802,7 +802,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>0.18959733</v>
+        <v>0.16351915</v>
       </c>
     </row>
     <row r="45">
@@ -810,7 +810,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>0.18690368</v>
+        <v>0.16142211</v>
       </c>
     </row>
     <row r="46">
@@ -818,7 +818,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>0.18432046</v>
+        <v>0.15943341</v>
       </c>
     </row>
     <row r="47">
@@ -826,7 +826,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>0.18184235</v>
+        <v>0.15754697</v>
       </c>
     </row>
     <row r="48">
@@ -834,7 +834,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>0.17946435</v>
+        <v>0.15575708</v>
       </c>
     </row>
     <row r="49">
@@ -842,7 +842,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>0.17718176</v>
+        <v>0.1540584</v>
       </c>
     </row>
     <row r="50">
@@ -850,7 +850,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>0.17499013</v>
+        <v>0.1524459</v>
       </c>
     </row>
     <row r="51">
@@ -858,7 +858,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>0.17288527</v>
+        <v>0.15091488</v>
       </c>
     </row>
     <row r="52">
@@ -866,7 +866,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>0.1708632</v>
+        <v>0.1494609</v>
       </c>
     </row>
     <row r="53">
@@ -874,7 +874,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>0.1689202</v>
+        <v>0.14807983</v>
       </c>
     </row>
     <row r="54">
@@ -882,7 +882,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>0.16705272</v>
+        <v>0.14676774</v>
       </c>
     </row>
     <row r="55">
@@ -890,7 +890,7 @@
         <v>54</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>0.16525742</v>
+        <v>0.14552096</v>
       </c>
     </row>
     <row r="56">
@@ -898,7 +898,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>0.16353112</v>
+        <v>0.14433604</v>
       </c>
     </row>
     <row r="57">
@@ -906,7 +906,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>0.16187083</v>
+        <v>0.14320971</v>
       </c>
     </row>
     <row r="58">
@@ -914,7 +914,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>0.1602737</v>
+        <v>0.1421389</v>
       </c>
     </row>
     <row r="59">
@@ -922,7 +922,7 @@
         <v>58</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>0.15873702</v>
+        <v>0.14112073</v>
       </c>
     </row>
     <row r="60">
@@ -930,7 +930,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>0.15725825</v>
+        <v>0.14015245</v>
       </c>
     </row>
     <row r="61">
@@ -938,7 +938,7 @@
         <v>60</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>0.15583493</v>
+        <v>0.1392315</v>
       </c>
     </row>
     <row r="62">
@@ -946,7 +946,7 @@
         <v>61</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>0.15446476</v>
+        <v>0.13835546</v>
       </c>
     </row>
     <row r="63">
@@ -954,7 +954,7 @@
         <v>62</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>0.15314555</v>
+        <v>0.13752201</v>
       </c>
     </row>
     <row r="64">
@@ -962,7 +962,7 @@
         <v>63</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>0.1518752</v>
+        <v>0.136729</v>
       </c>
     </row>
     <row r="65">
@@ -970,7 +970,7 @@
         <v>64</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>0.15065172</v>
+        <v>0.13597438</v>
       </c>
     </row>
     <row r="66">
@@ -978,7 +978,7 @@
         <v>65</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>0.14947322</v>
+        <v>0.1352562</v>
       </c>
     </row>
     <row r="67">
@@ -986,7 +986,7 @@
         <v>66</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>0.14833788</v>
+        <v>0.13457265</v>
       </c>
     </row>
     <row r="68">
@@ -994,7 +994,7 @@
         <v>67</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>0.147244</v>
+        <v>0.13392198</v>
       </c>
     </row>
     <row r="69">
@@ -1002,7 +1002,7 @@
         <v>68</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>0.14618991</v>
+        <v>0.13330255</v>
       </c>
     </row>
     <row r="70">
@@ -1010,7 +1010,7 @@
         <v>69</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>0.14517407</v>
+        <v>0.13271282</v>
       </c>
     </row>
     <row r="71">
@@ -1018,7 +1018,7 @@
         <v>70</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>0.14419497</v>
+        <v>0.13215131</v>
       </c>
     </row>
     <row r="72">
@@ -1026,7 +1026,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>0.14325118</v>
+        <v>0.13161663</v>
       </c>
     </row>
     <row r="73">
@@ -1034,7 +1034,7 @@
         <v>72</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>0.14234133</v>
+        <v>0.13110745</v>
       </c>
     </row>
     <row r="74">
@@ -1042,7 +1042,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>0.14146413</v>
+        <v>0.13062253</v>
       </c>
     </row>
     <row r="75">
@@ -1050,7 +1050,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>0.14061832</v>
+        <v>0.13016068</v>
       </c>
     </row>
     <row r="76">
@@ -1058,7 +1058,7 @@
         <v>75</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>0.1398027</v>
+        <v>0.12972077</v>
       </c>
     </row>
     <row r="77">
@@ -1066,7 +1066,7 @@
         <v>76</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>0.13901614</v>
+        <v>0.12930174</v>
       </c>
     </row>
     <row r="78">
@@ -1074,7 +1074,7 @@
         <v>77</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>0.13825753</v>
+        <v>0.12890257</v>
       </c>
     </row>
     <row r="79">
@@ -1082,7 +1082,7 @@
         <v>78</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>0.13752583</v>
+        <v>0.12852229</v>
       </c>
     </row>
     <row r="80">
@@ -1090,7 +1090,7 @@
         <v>79</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>0.13682004</v>
+        <v>0.12816</v>
       </c>
     </row>
     <row r="81">
@@ -1098,7 +1098,7 @@
         <v>80</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>0.13613918</v>
+        <v>0.12781483</v>
       </c>
     </row>
     <row r="82">
@@ -1106,7 +1106,7 @@
         <v>81</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>0.13548234</v>
+        <v>0.12748596</v>
       </c>
     </row>
     <row r="83">
@@ -1114,7 +1114,7 @@
         <v>82</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>0.13484862</v>
+        <v>0.12717259</v>
       </c>
     </row>
     <row r="84">
@@ -1122,7 +1122,7 @@
         <v>83</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>0.13423719</v>
+        <v>0.12687399</v>
       </c>
     </row>
     <row r="85">
@@ -1130,7 +1130,7 @@
         <v>84</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>0.13364721</v>
+        <v>0.12658946</v>
       </c>
     </row>
     <row r="86">
@@ -1138,7 +1138,7 @@
         <v>85</v>
       </c>
       <c r="B86" s="2" t="n">
-        <v>0.13307791</v>
+        <v>0.12631831</v>
       </c>
     </row>
     <row r="87">
@@ -1146,7 +1146,7 @@
         <v>86</v>
       </c>
       <c r="B87" s="2" t="n">
-        <v>0.13252854</v>
+        <v>0.12605991</v>
       </c>
     </row>
     <row r="88">
@@ -1154,7 +1154,7 @@
         <v>87</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>0.13199837</v>
+        <v>0.12581366</v>
       </c>
     </row>
     <row r="89">
@@ -1162,7 +1162,7 @@
         <v>88</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>0.1314867</v>
+        <v>0.12557897</v>
       </c>
     </row>
     <row r="90">
@@ -1170,7 +1170,7 @@
         <v>89</v>
       </c>
       <c r="B90" s="2" t="n">
-        <v>0.13099288</v>
+        <v>0.1253553</v>
       </c>
     </row>
     <row r="91">
@@ -1178,7 +1178,7 @@
         <v>90</v>
       </c>
       <c r="B91" s="2" t="n">
-        <v>0.13051625</v>
+        <v>0.12514213</v>
       </c>
     </row>
     <row r="92">
@@ -1186,7 +1186,7 @@
         <v>91</v>
       </c>
       <c r="B92" s="2" t="n">
-        <v>0.1300562</v>
+        <v>0.12493895</v>
       </c>
     </row>
     <row r="93">
@@ -1194,7 +1194,7 @@
         <v>92</v>
       </c>
       <c r="B93" s="2" t="n">
-        <v>0.12961213</v>
+        <v>0.12474529</v>
       </c>
     </row>
     <row r="94">
@@ -1202,7 +1202,7 @@
         <v>93</v>
       </c>
       <c r="B94" s="2" t="n">
-        <v>0.12918348</v>
+        <v>0.12456071</v>
       </c>
     </row>
     <row r="95">
@@ -1210,7 +1210,7 @@
         <v>94</v>
       </c>
       <c r="B95" s="2" t="n">
-        <v>0.1287697</v>
+        <v>0.12438477</v>
       </c>
     </row>
     <row r="96">
@@ -1218,7 +1218,7 @@
         <v>95</v>
       </c>
       <c r="B96" s="2" t="n">
-        <v>0.12837026</v>
+        <v>0.12421708</v>
       </c>
     </row>
     <row r="97">
@@ -1226,7 +1226,7 @@
         <v>96</v>
       </c>
       <c r="B97" s="2" t="n">
-        <v>0.12798464</v>
+        <v>0.12405723</v>
       </c>
     </row>
     <row r="98">
@@ -1234,7 +1234,7 @@
         <v>97</v>
       </c>
       <c r="B98" s="2" t="n">
-        <v>0.12761237</v>
+        <v>0.12390486</v>
       </c>
     </row>
     <row r="99">
@@ -1242,7 +1242,7 @@
         <v>98</v>
       </c>
       <c r="B99" s="2" t="n">
-        <v>0.12725296</v>
+        <v>0.12375962</v>
       </c>
     </row>
     <row r="100">
@@ -1250,7 +1250,7 @@
         <v>99</v>
       </c>
       <c r="B100" s="2" t="n">
-        <v>0.12690596</v>
+        <v>0.12362117</v>
       </c>
     </row>
     <row r="101">
@@ -1258,7 +1258,7 @@
         <v>100</v>
       </c>
       <c r="B101" s="2" t="n">
-        <v>0.12657095</v>
+        <v>0.1234892</v>
       </c>
     </row>
     <row r="102">
@@ -1266,7 +1266,7 @@
         <v>101</v>
       </c>
       <c r="B102" s="2" t="n">
-        <v>0.12624748</v>
+        <v>0.1233634</v>
       </c>
     </row>
     <row r="103">
@@ -1274,7 +1274,7 @@
         <v>102</v>
       </c>
       <c r="B103" s="2" t="n">
-        <v>0.12593517</v>
+        <v>0.12324348</v>
       </c>
     </row>
     <row r="104">
@@ -1282,7 +1282,7 @@
         <v>103</v>
       </c>
       <c r="B104" s="2" t="n">
-        <v>0.12563362</v>
+        <v>0.12312917</v>
       </c>
     </row>
     <row r="105">
@@ -1290,7 +1290,7 @@
         <v>104</v>
       </c>
       <c r="B105" s="2" t="n">
-        <v>0.12534244</v>
+        <v>0.12302019</v>
       </c>
     </row>
     <row r="106">
@@ -1298,7 +1298,7 @@
         <v>105</v>
       </c>
       <c r="B106" s="2" t="n">
-        <v>0.12506129</v>
+        <v>0.12291632</v>
       </c>
     </row>
     <row r="107">
@@ -1306,7 +1306,7 @@
         <v>106</v>
       </c>
       <c r="B107" s="2" t="n">
-        <v>0.12478981</v>
+        <v>0.12281729</v>
       </c>
     </row>
     <row r="108">
@@ -1314,7 +1314,7 @@
         <v>107</v>
       </c>
       <c r="B108" s="2" t="n">
-        <v>0.12452766</v>
+        <v>0.12272289</v>
       </c>
     </row>
     <row r="109">
@@ -1322,7 +1322,7 @@
         <v>108</v>
       </c>
       <c r="B109" s="2" t="n">
-        <v>0.12427452</v>
+        <v>0.12263291</v>
       </c>
     </row>
     <row r="110">
@@ -1330,7 +1330,7 @@
         <v>109</v>
       </c>
       <c r="B110" s="2" t="n">
-        <v>0.12403007</v>
+        <v>0.12254713</v>
       </c>
     </row>
     <row r="111">
@@ -1338,7 +1338,7 @@
         <v>110</v>
       </c>
       <c r="B111" s="2" t="n">
-        <v>0.12379401</v>
+        <v>0.12246536</v>
       </c>
     </row>
     <row r="112">
@@ -1346,7 +1346,7 @@
         <v>111</v>
       </c>
       <c r="B112" s="2" t="n">
-        <v>0.12356605</v>
+        <v>0.12238741</v>
       </c>
     </row>
     <row r="113">
@@ -1354,7 +1354,7 @@
         <v>112</v>
       </c>
       <c r="B113" s="2" t="n">
-        <v>0.12334591</v>
+        <v>0.1223131</v>
       </c>
     </row>
     <row r="114">
@@ -1362,7 +1362,7 @@
         <v>113</v>
       </c>
       <c r="B114" s="2" t="n">
-        <v>0.12313332</v>
+        <v>0.12224227</v>
       </c>
     </row>
     <row r="115">
@@ -1370,7 +1370,7 @@
         <v>114</v>
       </c>
       <c r="B115" s="2" t="n">
-        <v>0.12292802</v>
+        <v>0.12217474</v>
       </c>
     </row>
     <row r="116">
@@ -1378,7 +1378,7 @@
         <v>115</v>
       </c>
       <c r="B116" s="2" t="n">
-        <v>0.12272975</v>
+        <v>0.12211038</v>
       </c>
     </row>
     <row r="117">
@@ -1386,7 +1386,7 @@
         <v>116</v>
       </c>
       <c r="B117" s="2" t="n">
-        <v>0.12253828</v>
+        <v>0.12204902</v>
       </c>
     </row>
     <row r="118">
@@ -1394,7 +1394,7 @@
         <v>117</v>
       </c>
       <c r="B118" s="2" t="n">
-        <v>0.12235336</v>
+        <v>0.12199054</v>
       </c>
     </row>
     <row r="119">
@@ -1402,7 +1402,7 @@
         <v>118</v>
       </c>
       <c r="B119" s="2" t="n">
-        <v>0.12217477</v>
+        <v>0.12193479</v>
       </c>
     </row>
     <row r="120">
@@ -1410,7 +1410,7 @@
         <v>119</v>
       </c>
       <c r="B120" s="2" t="n">
-        <v>0.12200229</v>
+        <v>0.12188164</v>
       </c>
     </row>
     <row r="121">
@@ -1418,7 +1418,7 @@
         <v>120</v>
       </c>
       <c r="B121" s="2" t="n">
-        <v>0.12183572</v>
+        <v>0.12183099</v>
       </c>
     </row>
     <row r="122">
@@ -1426,7 +1426,7 @@
         <v>121</v>
       </c>
       <c r="B122" s="2" t="n">
-        <v>0.12167484</v>
+        <v>0.1217827</v>
       </c>
     </row>
     <row r="123">
@@ -1434,7 +1434,7 @@
         <v>122</v>
       </c>
       <c r="B123" s="2" t="n">
-        <v>0.12151947</v>
+        <v>0.12173668</v>
       </c>
     </row>
     <row r="124">
@@ -1442,7 +1442,7 @@
         <v>123</v>
       </c>
       <c r="B124" s="2" t="n">
-        <v>0.12136941</v>
+        <v>0.12169281</v>
       </c>
     </row>
     <row r="125">
@@ -1450,7 +1450,7 @@
         <v>124</v>
       </c>
       <c r="B125" s="2" t="n">
-        <v>0.12122448</v>
+        <v>0.12165099</v>
       </c>
     </row>
     <row r="126">
@@ -1458,7 +1458,7 @@
         <v>125</v>
       </c>
       <c r="B126" s="2" t="n">
-        <v>0.1210845</v>
+        <v>0.12161113</v>
       </c>
     </row>
     <row r="127">
@@ -1466,7 +1466,7 @@
         <v>126</v>
       </c>
       <c r="B127" s="2" t="n">
-        <v>0.12094931</v>
+        <v>0.12157314</v>
       </c>
     </row>
     <row r="128">
@@ -1474,7 +1474,7 @@
         <v>127</v>
       </c>
       <c r="B128" s="2" t="n">
-        <v>0.12081873</v>
+        <v>0.12153694</v>
       </c>
     </row>
     <row r="129">
@@ -1482,7 +1482,7 @@
         <v>128</v>
       </c>
       <c r="B129" s="2" t="n">
-        <v>0.12069262</v>
+        <v>0.12150243</v>
       </c>
     </row>
     <row r="130">
@@ -1490,7 +1490,7 @@
         <v>129</v>
       </c>
       <c r="B130" s="2" t="n">
-        <v>0.12057081</v>
+        <v>0.12146953</v>
       </c>
     </row>
     <row r="131">
@@ -1498,7 +1498,7 @@
         <v>130</v>
       </c>
       <c r="B131" s="2" t="n">
-        <v>0.12045316</v>
+        <v>0.12143819</v>
       </c>
     </row>
     <row r="132">
@@ -1506,7 +1506,7 @@
         <v>131</v>
       </c>
       <c r="B132" s="2" t="n">
-        <v>0.12033953</v>
+        <v>0.12140831</v>
       </c>
     </row>
     <row r="133">
@@ -1514,7 +1514,7 @@
         <v>132</v>
       </c>
       <c r="B133" s="2" t="n">
-        <v>0.12022978</v>
+        <v>0.12137984</v>
       </c>
     </row>
     <row r="134">
@@ -1522,7 +1522,7 @@
         <v>133</v>
       </c>
       <c r="B134" s="2" t="n">
-        <v>0.12012378</v>
+        <v>0.1213527</v>
       </c>
     </row>
     <row r="135">
@@ -1530,7 +1530,7 @@
         <v>134</v>
       </c>
       <c r="B135" s="2" t="n">
-        <v>0.12002139</v>
+        <v>0.12132684</v>
       </c>
     </row>
     <row r="136">
@@ -1538,7 +1538,7 @@
         <v>135</v>
       </c>
       <c r="B136" s="2" t="n">
-        <v>0.1199225</v>
+        <v>0.1213022</v>
       </c>
     </row>
     <row r="137">
@@ -1546,7 +1546,7 @@
         <v>136</v>
       </c>
       <c r="B137" s="2" t="n">
-        <v>0.11982698</v>
+        <v>0.12127871</v>
       </c>
     </row>
     <row r="138">
@@ -1554,7 +1554,7 @@
         <v>137</v>
       </c>
       <c r="B138" s="2" t="n">
-        <v>0.11973472</v>
+        <v>0.12125633</v>
       </c>
     </row>
     <row r="139">
@@ -1562,7 +1562,7 @@
         <v>138</v>
       </c>
       <c r="B139" s="2" t="n">
-        <v>0.1196456</v>
+        <v>0.12123501</v>
       </c>
     </row>
     <row r="140">
@@ -1570,7 +1570,7 @@
         <v>139</v>
       </c>
       <c r="B140" s="2" t="n">
-        <v>0.11955953</v>
+        <v>0.12121468</v>
       </c>
     </row>
     <row r="141">
@@ -1578,7 +1578,7 @@
         <v>140</v>
       </c>
       <c r="B141" s="2" t="n">
-        <v>0.11947639</v>
+        <v>0.12119532</v>
       </c>
     </row>
     <row r="142">
@@ -1586,7 +1586,7 @@
         <v>141</v>
       </c>
       <c r="B142" s="2" t="n">
-        <v>0.11939609</v>
+        <v>0.12117687</v>
       </c>
     </row>
     <row r="143">
@@ -1594,7 +1594,7 @@
         <v>142</v>
       </c>
       <c r="B143" s="2" t="n">
-        <v>0.11931853</v>
+        <v>0.12115929</v>
       </c>
     </row>
     <row r="144">
@@ -1602,7 +1602,7 @@
         <v>143</v>
       </c>
       <c r="B144" s="2" t="n">
-        <v>0.11924361</v>
+        <v>0.12114254</v>
       </c>
     </row>
     <row r="145">
@@ -1610,7 +1610,7 @@
         <v>144</v>
       </c>
       <c r="B145" s="2" t="n">
-        <v>0.11917125</v>
+        <v>0.12112658</v>
       </c>
     </row>
     <row r="146">
@@ -1618,7 +1618,7 @@
         <v>145</v>
       </c>
       <c r="B146" s="2" t="n">
-        <v>0.11910135</v>
+        <v>0.12111138</v>
       </c>
     </row>
     <row r="147">
@@ -1626,7 +1626,7 @@
         <v>146</v>
       </c>
       <c r="B147" s="2" t="n">
-        <v>0.11903383</v>
+        <v>0.12109689</v>
       </c>
     </row>
     <row r="148">
@@ -1634,7 +1634,7 @@
         <v>147</v>
       </c>
       <c r="B148" s="2" t="n">
-        <v>0.11896862</v>
+        <v>0.12108309</v>
       </c>
     </row>
     <row r="149">
@@ -1642,7 +1642,7 @@
         <v>148</v>
       </c>
       <c r="B149" s="2" t="n">
-        <v>0.11890563</v>
+        <v>0.12106995</v>
       </c>
     </row>
     <row r="150">
@@ -1650,7 +1650,7 @@
         <v>149</v>
       </c>
       <c r="B150" s="2" t="n">
-        <v>0.11884479</v>
+        <v>0.12105742</v>
       </c>
     </row>
     <row r="151">
@@ -1658,7 +1658,7 @@
         <v>150</v>
       </c>
       <c r="B151" s="2" t="n">
-        <v>0.11878602</v>
+        <v>0.12104549</v>
       </c>
     </row>
     <row r="152">
@@ -1666,7 +1666,7 @@
         <v>151</v>
       </c>
       <c r="B152" s="2" t="n">
-        <v>0.11872925</v>
+        <v>0.12103413</v>
       </c>
     </row>
     <row r="153">
@@ -1674,7 +1674,7 @@
         <v>152</v>
       </c>
       <c r="B153" s="2" t="n">
-        <v>0.11867442</v>
+        <v>0.12102331</v>
       </c>
     </row>
     <row r="154">
@@ -1682,7 +1682,7 @@
         <v>153</v>
       </c>
       <c r="B154" s="2" t="n">
-        <v>0.11862145</v>
+        <v>0.121013</v>
       </c>
     </row>
     <row r="155">
@@ -1690,7 +1690,7 @@
         <v>154</v>
       </c>
       <c r="B155" s="2" t="n">
-        <v>0.11857029</v>
+        <v>0.12100318</v>
       </c>
     </row>
     <row r="156">
@@ -1698,7 +1698,7 @@
         <v>155</v>
       </c>
       <c r="B156" s="2" t="n">
-        <v>0.11852088</v>
+        <v>0.12099383</v>
       </c>
     </row>
     <row r="157">
@@ -1706,7 +1706,7 @@
         <v>156</v>
       </c>
       <c r="B157" s="2" t="n">
-        <v>0.11847314</v>
+        <v>0.12098492</v>
       </c>
     </row>
     <row r="158">
@@ -1714,7 +1714,7 @@
         <v>157</v>
       </c>
       <c r="B158" s="2" t="n">
-        <v>0.11842704</v>
+        <v>0.12097644</v>
       </c>
     </row>
     <row r="159">
@@ -1722,7 +1722,7 @@
         <v>158</v>
       </c>
       <c r="B159" s="2" t="n">
-        <v>0.1183825</v>
+        <v>0.12096836</v>
       </c>
     </row>
     <row r="160">
@@ -1730,7 +1730,7 @@
         <v>159</v>
       </c>
       <c r="B160" s="2" t="n">
-        <v>0.11833948</v>
+        <v>0.12096067</v>
       </c>
     </row>
     <row r="161">
@@ -1738,7 +1738,7 @@
         <v>160</v>
       </c>
       <c r="B161" s="2" t="n">
-        <v>0.11829793</v>
+        <v>0.12095335</v>
       </c>
     </row>
     <row r="162">
@@ -1746,7 +1746,7 @@
         <v>161</v>
       </c>
       <c r="B162" s="2" t="n">
-        <v>0.11825779</v>
+        <v>0.12094638</v>
       </c>
     </row>
     <row r="163">
@@ -1754,7 +1754,7 @@
         <v>162</v>
       </c>
       <c r="B163" s="2" t="n">
-        <v>0.11821902</v>
+        <v>0.12093974</v>
       </c>
     </row>
     <row r="164">
@@ -1762,7 +1762,7 @@
         <v>163</v>
       </c>
       <c r="B164" s="2" t="n">
-        <v>0.11818156</v>
+        <v>0.12093342</v>
       </c>
     </row>
     <row r="165">
@@ -1770,7 +1770,7 @@
         <v>164</v>
       </c>
       <c r="B165" s="2" t="n">
-        <v>0.11814539</v>
+        <v>0.1209274</v>
       </c>
     </row>
     <row r="166">
@@ -1778,7 +1778,7 @@
         <v>165</v>
       </c>
       <c r="B166" s="2" t="n">
-        <v>0.11811045</v>
+        <v>0.12092168</v>
       </c>
     </row>
     <row r="167">
@@ -1786,7 +1786,7 @@
         <v>166</v>
       </c>
       <c r="B167" s="2" t="n">
-        <v>0.11807669</v>
+        <v>0.12091622</v>
       </c>
     </row>
     <row r="168">
@@ -1794,7 +1794,7 @@
         <v>167</v>
       </c>
       <c r="B168" s="2" t="n">
-        <v>0.11804409</v>
+        <v>0.12091103</v>
       </c>
     </row>
     <row r="169">
@@ -1802,7 +1802,7 @@
         <v>168</v>
       </c>
       <c r="B169" s="2" t="n">
-        <v>0.11801259</v>
+        <v>0.1209061</v>
       </c>
     </row>
     <row r="170">
@@ -1810,7 +1810,7 @@
         <v>169</v>
       </c>
       <c r="B170" s="2" t="n">
-        <v>0.11798217</v>
+        <v>0.12090139</v>
       </c>
     </row>
     <row r="171">
@@ -1818,7 +1818,7 @@
         <v>170</v>
       </c>
       <c r="B171" s="2" t="n">
-        <v>0.11795278</v>
+        <v>0.12089692</v>
       </c>
     </row>
     <row r="172">
@@ -1826,7 +1826,7 @@
         <v>171</v>
       </c>
       <c r="B172" s="2" t="n">
-        <v>0.1179244</v>
+        <v>0.12089266</v>
       </c>
     </row>
     <row r="173">
@@ -1834,7 +1834,7 @@
         <v>172</v>
       </c>
       <c r="B173" s="2" t="n">
-        <v>0.11789698</v>
+        <v>0.12088861</v>
       </c>
     </row>
     <row r="174">
@@ -1842,7 +1842,7 @@
         <v>173</v>
       </c>
       <c r="B174" s="2" t="n">
-        <v>0.11787049</v>
+        <v>0.12088476</v>
       </c>
     </row>
     <row r="175">
@@ -1850,7 +1850,7 @@
         <v>174</v>
       </c>
       <c r="B175" s="2" t="n">
-        <v>0.11784491</v>
+        <v>0.12088109</v>
       </c>
     </row>
     <row r="176">
@@ -1858,7 +1858,7 @@
         <v>175</v>
       </c>
       <c r="B176" s="2" t="n">
-        <v>0.1178202</v>
+        <v>0.1208776</v>
       </c>
     </row>
     <row r="177">
@@ -1866,7 +1866,7 @@
         <v>176</v>
       </c>
       <c r="B177" s="2" t="n">
-        <v>0.11779632</v>
+        <v>0.12087429</v>
       </c>
     </row>
     <row r="178">
@@ -1874,7 +1874,7 @@
         <v>177</v>
       </c>
       <c r="B178" s="2" t="n">
-        <v>0.11777326</v>
+        <v>0.12087113</v>
       </c>
     </row>
     <row r="179">
@@ -1882,7 +1882,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="2" t="n">
-        <v>0.11775099</v>
+        <v>0.12086813</v>
       </c>
     </row>
     <row r="180">
@@ -1890,7 +1890,7 @@
         <v>179</v>
       </c>
       <c r="B180" s="2" t="n">
-        <v>0.11772947</v>
+        <v>0.12086527</v>
       </c>
     </row>
     <row r="181">
@@ -1898,7 +1898,7 @@
         <v>180</v>
       </c>
       <c r="B181" s="2" t="n">
-        <v>0.11770869</v>
+        <v>0.12086256</v>
       </c>
     </row>
     <row r="182">
@@ -1906,7 +1906,7 @@
         <v>181</v>
       </c>
       <c r="B182" s="2" t="n">
-        <v>0.11768861</v>
+        <v>0.12085997</v>
       </c>
     </row>
     <row r="183">
@@ -1914,7 +1914,7 @@
         <v>182</v>
       </c>
       <c r="B183" s="2" t="n">
-        <v>0.11766922</v>
+        <v>0.12085752</v>
       </c>
     </row>
     <row r="184">
@@ -1922,7 +1922,7 @@
         <v>183</v>
       </c>
       <c r="B184" s="2" t="n">
-        <v>0.11765049</v>
+        <v>0.12085519</v>
       </c>
     </row>
     <row r="185">
@@ -1930,7 +1930,7 @@
         <v>184</v>
       </c>
       <c r="B185" s="2" t="n">
-        <v>0.11763239</v>
+        <v>0.12085297</v>
       </c>
     </row>
     <row r="186">
@@ -1938,7 +1938,7 @@
         <v>185</v>
       </c>
       <c r="B186" s="2" t="n">
-        <v>0.11761491</v>
+        <v>0.12085086</v>
       </c>
     </row>
     <row r="187">
@@ -1946,7 +1946,7 @@
         <v>186</v>
       </c>
       <c r="B187" s="2" t="n">
-        <v>0.11759802</v>
+        <v>0.12084885</v>
       </c>
     </row>
     <row r="188">
@@ -1954,7 +1954,7 @@
         <v>187</v>
       </c>
       <c r="B188" s="2" t="n">
-        <v>0.11758171</v>
+        <v>0.12084695</v>
       </c>
     </row>
     <row r="189">
@@ -1962,7 +1962,7 @@
         <v>188</v>
       </c>
       <c r="B189" s="2" t="n">
-        <v>0.11756596</v>
+        <v>0.12084514</v>
       </c>
     </row>
     <row r="190">
@@ -1970,7 +1970,7 @@
         <v>189</v>
       </c>
       <c r="B190" s="2" t="n">
-        <v>0.11755074</v>
+        <v>0.12084342</v>
       </c>
     </row>
     <row r="191">
@@ -1978,7 +1978,7 @@
         <v>190</v>
       </c>
       <c r="B191" s="2" t="n">
-        <v>0.11753604</v>
+        <v>0.12084178</v>
       </c>
     </row>
     <row r="192">
@@ -1986,7 +1986,7 @@
         <v>191</v>
       </c>
       <c r="B192" s="2" t="n">
-        <v>0.11752184</v>
+        <v>0.12084023</v>
       </c>
     </row>
     <row r="193">
@@ -1994,7 +1994,7 @@
         <v>192</v>
       </c>
       <c r="B193" s="2" t="n">
-        <v>0.11750812</v>
+        <v>0.12083876</v>
       </c>
     </row>
     <row r="194">
@@ -2002,7 +2002,7 @@
         <v>193</v>
       </c>
       <c r="B194" s="2" t="n">
-        <v>0.11749487</v>
+        <v>0.12083736</v>
       </c>
     </row>
     <row r="195">
@@ -2010,7 +2010,7 @@
         <v>194</v>
       </c>
       <c r="B195" s="2" t="n">
-        <v>0.11748206</v>
+        <v>0.12083603</v>
       </c>
     </row>
     <row r="196">
@@ -2018,7 +2018,7 @@
         <v>195</v>
       </c>
       <c r="B196" s="2" t="n">
-        <v>0.1174697</v>
+        <v>0.12083477</v>
       </c>
     </row>
     <row r="197">
@@ -2026,7 +2026,7 @@
         <v>196</v>
       </c>
       <c r="B197" s="2" t="n">
-        <v>0.11745775</v>
+        <v>0.12083357</v>
       </c>
     </row>
     <row r="198">
@@ -2034,7 +2034,7 @@
         <v>197</v>
       </c>
       <c r="B198" s="2" t="n">
-        <v>0.11744622</v>
+        <v>0.12083243</v>
       </c>
     </row>
     <row r="199">
@@ -2042,7 +2042,7 @@
         <v>198</v>
       </c>
       <c r="B199" s="2" t="n">
-        <v>0.11743507</v>
+        <v>0.12083135</v>
       </c>
     </row>
     <row r="200">
@@ -2050,7 +2050,7 @@
         <v>199</v>
       </c>
       <c r="B200" s="2" t="n">
-        <v>0.1174243</v>
+        <v>0.12083033</v>
       </c>
     </row>
     <row r="201">
@@ -2058,7 +2058,7 @@
         <v>200</v>
       </c>
       <c r="B201" s="2" t="n">
-        <v>0.1174139</v>
+        <v>0.12082936</v>
       </c>
     </row>
     <row r="202">
@@ -2066,7 +2066,7 @@
         <v>201</v>
       </c>
       <c r="B202" s="2" t="n">
-        <v>0.11740386</v>
+        <v>0.12082844</v>
       </c>
     </row>
     <row r="203">
@@ -2074,7 +2074,7 @@
         <v>202</v>
       </c>
       <c r="B203" s="2" t="n">
-        <v>0.11739415</v>
+        <v>0.12082756</v>
       </c>
     </row>
     <row r="204">
@@ -2082,7 +2082,7 @@
         <v>203</v>
       </c>
       <c r="B204" s="2" t="n">
-        <v>0.11738477</v>
+        <v>0.12082673</v>
       </c>
     </row>
     <row r="205">
@@ -2090,7 +2090,7 @@
         <v>204</v>
       </c>
       <c r="B205" s="2" t="n">
-        <v>0.11737572</v>
+        <v>0.12082595</v>
       </c>
     </row>
     <row r="206">
@@ -2098,7 +2098,7 @@
         <v>205</v>
       </c>
       <c r="B206" s="2" t="n">
-        <v>0.11736697</v>
+        <v>0.1208252</v>
       </c>
     </row>
     <row r="207">
@@ -2106,7 +2106,7 @@
         <v>206</v>
       </c>
       <c r="B207" s="2" t="n">
-        <v>0.11735852</v>
+        <v>0.1208245</v>
       </c>
     </row>
     <row r="208">
@@ -2114,7 +2114,7 @@
         <v>207</v>
       </c>
       <c r="B208" s="2" t="n">
-        <v>0.11735036</v>
+        <v>0.12082383</v>
       </c>
     </row>
     <row r="209">
@@ -2122,7 +2122,7 @@
         <v>208</v>
       </c>
       <c r="B209" s="2" t="n">
-        <v>0.11734247</v>
+        <v>0.12082319</v>
       </c>
     </row>
     <row r="210">
@@ -2130,7 +2130,7 @@
         <v>209</v>
       </c>
       <c r="B210" s="2" t="n">
-        <v>0.11733485</v>
+        <v>0.12082259</v>
       </c>
     </row>
     <row r="211">
@@ -2138,7 +2138,7 @@
         <v>210</v>
       </c>
       <c r="B211" s="2" t="n">
-        <v>0.11732749</v>
+        <v>0.12082203</v>
       </c>
     </row>
     <row r="212">
@@ -2146,7 +2146,7 @@
         <v>211</v>
       </c>
       <c r="B212" s="2" t="n">
-        <v>0.11732038</v>
+        <v>0.12082149</v>
       </c>
     </row>
     <row r="213">
@@ -2154,7 +2154,7 @@
         <v>212</v>
       </c>
       <c r="B213" s="2" t="n">
-        <v>0.11731352</v>
+        <v>0.12082098</v>
       </c>
     </row>
     <row r="214">
@@ -2162,7 +2162,7 @@
         <v>213</v>
       </c>
       <c r="B214" s="2" t="n">
-        <v>0.11730688</v>
+        <v>0.1208205</v>
       </c>
     </row>
     <row r="215">
@@ -2170,7 +2170,7 @@
         <v>214</v>
       </c>
       <c r="B215" s="2" t="n">
-        <v>0.11730047</v>
+        <v>0.12082004</v>
       </c>
     </row>
     <row r="216">
@@ -2178,7 +2178,7 @@
         <v>215</v>
       </c>
       <c r="B216" s="2" t="n">
-        <v>0.11729428</v>
+        <v>0.12081961</v>
       </c>
     </row>
     <row r="217">
@@ -2186,7 +2186,7 @@
         <v>216</v>
       </c>
       <c r="B217" s="2" t="n">
-        <v>0.1172883</v>
+        <v>0.1208192</v>
       </c>
     </row>
     <row r="218">
@@ -2194,7 +2194,7 @@
         <v>217</v>
       </c>
       <c r="B218" s="2" t="n">
-        <v>0.11728253</v>
+        <v>0.12081882</v>
       </c>
     </row>
     <row r="219">
@@ -2202,7 +2202,7 @@
         <v>218</v>
       </c>
       <c r="B219" s="2" t="n">
-        <v>0.11727695</v>
+        <v>0.12081845</v>
       </c>
     </row>
     <row r="220">
@@ -2210,7 +2210,7 @@
         <v>219</v>
       </c>
       <c r="B220" s="2" t="n">
-        <v>0.11727156</v>
+        <v>0.12081811</v>
       </c>
     </row>
     <row r="221">
@@ -2218,7 +2218,7 @@
         <v>220</v>
       </c>
       <c r="B221" s="2" t="n">
-        <v>0.11726635</v>
+        <v>0.12081779</v>
       </c>
     </row>
     <row r="222">
@@ -2226,7 +2226,7 @@
         <v>221</v>
       </c>
       <c r="B222" s="2" t="n">
-        <v>0.11726132</v>
+        <v>0.12081748</v>
       </c>
     </row>
     <row r="223">
@@ -2234,7 +2234,7 @@
         <v>222</v>
       </c>
       <c r="B223" s="2" t="n">
-        <v>0.11725646</v>
+        <v>0.12081719</v>
       </c>
     </row>
     <row r="224">
@@ -2242,7 +2242,7 @@
         <v>223</v>
       </c>
       <c r="B224" s="2" t="n">
-        <v>0.11725176</v>
+        <v>0.12081692</v>
       </c>
     </row>
     <row r="225">
@@ -2250,7 +2250,7 @@
         <v>224</v>
       </c>
       <c r="B225" s="2" t="n">
-        <v>0.11724723</v>
+        <v>0.12081666</v>
       </c>
     </row>
     <row r="226">
@@ -2258,7 +2258,7 @@
         <v>225</v>
       </c>
       <c r="B226" s="2" t="n">
-        <v>0.11724285</v>
+        <v>0.12081642</v>
       </c>
     </row>
     <row r="227">
@@ -2266,7 +2266,7 @@
         <v>226</v>
       </c>
       <c r="B227" s="2" t="n">
-        <v>0.11723862</v>
+        <v>0.12081619</v>
       </c>
     </row>
     <row r="228">
@@ -2274,7 +2274,7 @@
         <v>227</v>
       </c>
       <c r="B228" s="2" t="n">
-        <v>0.11723453</v>
+        <v>0.12081598</v>
       </c>
     </row>
     <row r="229">
@@ -2282,7 +2282,7 @@
         <v>228</v>
       </c>
       <c r="B229" s="2" t="n">
-        <v>0.11723058</v>
+        <v>0.12081577</v>
       </c>
     </row>
     <row r="230">
@@ -2290,7 +2290,7 @@
         <v>229</v>
       </c>
       <c r="B230" s="2" t="n">
-        <v>0.11722676</v>
+        <v>0.12081558</v>
       </c>
     </row>
     <row r="231">
@@ -2298,7 +2298,7 @@
         <v>230</v>
       </c>
       <c r="B231" s="2" t="n">
-        <v>0.11722308</v>
+        <v>0.12081541</v>
       </c>
     </row>
     <row r="232">
@@ -2306,7 +2306,7 @@
         <v>231</v>
       </c>
       <c r="B232" s="2" t="n">
-        <v>0.11721952</v>
+        <v>0.12081524</v>
       </c>
     </row>
     <row r="233">
@@ -2314,7 +2314,7 @@
         <v>232</v>
       </c>
       <c r="B233" s="2" t="n">
-        <v>0.11721608</v>
+        <v>0.12081508</v>
       </c>
     </row>
     <row r="234">
@@ -2322,7 +2322,7 @@
         <v>233</v>
       </c>
       <c r="B234" s="2" t="n">
-        <v>0.11721276</v>
+        <v>0.12081493</v>
       </c>
     </row>
     <row r="235">
@@ -2330,7 +2330,7 @@
         <v>234</v>
       </c>
       <c r="B235" s="2" t="n">
-        <v>0.11720955</v>
+        <v>0.12081479</v>
       </c>
     </row>
     <row r="236">
@@ -2338,7 +2338,7 @@
         <v>235</v>
       </c>
       <c r="B236" s="2" t="n">
-        <v>0.11720644</v>
+        <v>0.12081466</v>
       </c>
     </row>
     <row r="237">
@@ -2346,7 +2346,7 @@
         <v>236</v>
       </c>
       <c r="B237" s="2" t="n">
-        <v>0.11720345</v>
+        <v>0.12081454</v>
       </c>
     </row>
     <row r="238">
@@ -2354,7 +2354,7 @@
         <v>237</v>
       </c>
       <c r="B238" s="2" t="n">
-        <v>0.11720055</v>
+        <v>0.12081443</v>
       </c>
     </row>
     <row r="239">
@@ -2362,7 +2362,7 @@
         <v>238</v>
       </c>
       <c r="B239" s="2" t="n">
-        <v>0.11719776</v>
+        <v>0.12081432</v>
       </c>
     </row>
     <row r="240">
@@ -2370,783 +2370,7 @@
         <v>239</v>
       </c>
       <c r="B240" s="2" t="n">
-        <v>0.11719506</v>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" s="2" t="n">
-        <v>240</v>
-      </c>
-      <c r="B241" s="2" t="n">
-        <v>0.11719245</v>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" s="2" t="n">
-        <v>241</v>
-      </c>
-      <c r="B242" s="2" t="n">
-        <v>0.11718993</v>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" s="2" t="n">
-        <v>242</v>
-      </c>
-      <c r="B243" s="2" t="n">
-        <v>0.11718749</v>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" s="2" t="n">
-        <v>243</v>
-      </c>
-      <c r="B244" s="2" t="n">
-        <v>0.11718514</v>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" s="2" t="n">
-        <v>244</v>
-      </c>
-      <c r="B245" s="2" t="n">
-        <v>0.11718287</v>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" s="2" t="n">
-        <v>245</v>
-      </c>
-      <c r="B246" s="2" t="n">
-        <v>0.11718067</v>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" s="2" t="n">
-        <v>246</v>
-      </c>
-      <c r="B247" s="2" t="n">
-        <v>0.11717855</v>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" s="2" t="n">
-        <v>247</v>
-      </c>
-      <c r="B248" s="2" t="n">
-        <v>0.1171765</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" s="2" t="n">
-        <v>248</v>
-      </c>
-      <c r="B249" s="2" t="n">
-        <v>0.11717452</v>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" s="2" t="n">
-        <v>249</v>
-      </c>
-      <c r="B250" s="2" t="n">
-        <v>0.11717261</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" s="2" t="n">
-        <v>250</v>
-      </c>
-      <c r="B251" s="2" t="n">
-        <v>0.11717076</v>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" s="2" t="n">
-        <v>251</v>
-      </c>
-      <c r="B252" s="2" t="n">
-        <v>0.11716898</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" s="2" t="n">
-        <v>252</v>
-      </c>
-      <c r="B253" s="2" t="n">
-        <v>0.11716725</v>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" s="2" t="n">
-        <v>253</v>
-      </c>
-      <c r="B254" s="2" t="n">
-        <v>0.11716559</v>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" s="2" t="n">
-        <v>254</v>
-      </c>
-      <c r="B255" s="2" t="n">
-        <v>0.11716398</v>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" s="2" t="n">
-        <v>255</v>
-      </c>
-      <c r="B256" s="2" t="n">
-        <v>0.11716242</v>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" s="2" t="n">
-        <v>256</v>
-      </c>
-      <c r="B257" s="2" t="n">
-        <v>0.11716092</v>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" s="2" t="n">
-        <v>257</v>
-      </c>
-      <c r="B258" s="2" t="n">
-        <v>0.11715947</v>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" s="2" t="n">
-        <v>258</v>
-      </c>
-      <c r="B259" s="2" t="n">
-        <v>0.11715807</v>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" s="2" t="n">
-        <v>259</v>
-      </c>
-      <c r="B260" s="2" t="n">
-        <v>0.11715671</v>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" s="2" t="n">
-        <v>260</v>
-      </c>
-      <c r="B261" s="2" t="n">
-        <v>0.1171554</v>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" s="2" t="n">
-        <v>261</v>
-      </c>
-      <c r="B262" s="2" t="n">
-        <v>0.11715414</v>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" s="2" t="n">
-        <v>262</v>
-      </c>
-      <c r="B263" s="2" t="n">
-        <v>0.11715292</v>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" s="2" t="n">
-        <v>263</v>
-      </c>
-      <c r="B264" s="2" t="n">
-        <v>0.11715174</v>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" s="2" t="n">
-        <v>264</v>
-      </c>
-      <c r="B265" s="2" t="n">
-        <v>0.1171506</v>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" s="2" t="n">
-        <v>265</v>
-      </c>
-      <c r="B266" s="2" t="n">
-        <v>0.1171495</v>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" s="2" t="n">
-        <v>266</v>
-      </c>
-      <c r="B267" s="2" t="n">
-        <v>0.11714843</v>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" s="2" t="n">
-        <v>267</v>
-      </c>
-      <c r="B268" s="2" t="n">
-        <v>0.11714741</v>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" s="2" t="n">
-        <v>268</v>
-      </c>
-      <c r="B269" s="2" t="n">
-        <v>0.11714641</v>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" s="2" t="n">
-        <v>269</v>
-      </c>
-      <c r="B270" s="2" t="n">
-        <v>0.11714545</v>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" s="2" t="n">
-        <v>270</v>
-      </c>
-      <c r="B271" s="2" t="n">
-        <v>0.11714453</v>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" s="2" t="n">
-        <v>271</v>
-      </c>
-      <c r="B272" s="2" t="n">
-        <v>0.11714363</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" s="2" t="n">
-        <v>272</v>
-      </c>
-      <c r="B273" s="2" t="n">
-        <v>0.11714276</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" s="2" t="n">
-        <v>273</v>
-      </c>
-      <c r="B274" s="2" t="n">
-        <v>0.11714193</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" s="2" t="n">
-        <v>274</v>
-      </c>
-      <c r="B275" s="2" t="n">
-        <v>0.11714112</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" s="2" t="n">
-        <v>275</v>
-      </c>
-      <c r="B276" s="2" t="n">
-        <v>0.11714034</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" s="2" t="n">
-        <v>276</v>
-      </c>
-      <c r="B277" s="2" t="n">
-        <v>0.11713959</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" s="2" t="n">
-        <v>277</v>
-      </c>
-      <c r="B278" s="2" t="n">
-        <v>0.11713886</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" s="2" t="n">
-        <v>278</v>
-      </c>
-      <c r="B279" s="2" t="n">
-        <v>0.11713815</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" s="2" t="n">
-        <v>279</v>
-      </c>
-      <c r="B280" s="2" t="n">
-        <v>0.11713747</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" s="2" t="n">
-        <v>280</v>
-      </c>
-      <c r="B281" s="2" t="n">
-        <v>0.11713682</v>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" s="2" t="n">
-        <v>281</v>
-      </c>
-      <c r="B282" s="2" t="n">
-        <v>0.11713618</v>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" s="2" t="n">
-        <v>282</v>
-      </c>
-      <c r="B283" s="2" t="n">
-        <v>0.11713557</v>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" s="2" t="n">
-        <v>283</v>
-      </c>
-      <c r="B284" s="2" t="n">
-        <v>0.11713497</v>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" s="2" t="n">
-        <v>284</v>
-      </c>
-      <c r="B285" s="2" t="n">
-        <v>0.1171344</v>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" s="2" t="n">
-        <v>285</v>
-      </c>
-      <c r="B286" s="2" t="n">
-        <v>0.11713385</v>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" s="2" t="n">
-        <v>286</v>
-      </c>
-      <c r="B287" s="2" t="n">
-        <v>0.11713331</v>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" s="2" t="n">
-        <v>287</v>
-      </c>
-      <c r="B288" s="2" t="n">
-        <v>0.1171328</v>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" s="2" t="n">
-        <v>288</v>
-      </c>
-      <c r="B289" s="2" t="n">
-        <v>0.1171323</v>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" s="2" t="n">
-        <v>289</v>
-      </c>
-      <c r="B290" s="2" t="n">
-        <v>0.11713181</v>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" s="2" t="n">
-        <v>290</v>
-      </c>
-      <c r="B291" s="2" t="n">
-        <v>0.11713135</v>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" s="2" t="n">
-        <v>291</v>
-      </c>
-      <c r="B292" s="2" t="n">
-        <v>0.1171309</v>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" s="2" t="n">
-        <v>292</v>
-      </c>
-      <c r="B293" s="2" t="n">
-        <v>0.11713046</v>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" s="2" t="n">
-        <v>293</v>
-      </c>
-      <c r="B294" s="2" t="n">
-        <v>0.11713004</v>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" s="2" t="n">
-        <v>294</v>
-      </c>
-      <c r="B295" s="2" t="n">
-        <v>0.11712964</v>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" s="2" t="n">
-        <v>295</v>
-      </c>
-      <c r="B296" s="2" t="n">
-        <v>0.11712924</v>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" s="2" t="n">
-        <v>296</v>
-      </c>
-      <c r="B297" s="2" t="n">
-        <v>0.11712886</v>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" s="2" t="n">
-        <v>297</v>
-      </c>
-      <c r="B298" s="2" t="n">
-        <v>0.1171285</v>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" s="2" t="n">
-        <v>298</v>
-      </c>
-      <c r="B299" s="2" t="n">
-        <v>0.11712814</v>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" s="2" t="n">
-        <v>299</v>
-      </c>
-      <c r="B300" s="2" t="n">
-        <v>0.1171278</v>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" s="2" t="n">
-        <v>300</v>
-      </c>
-      <c r="B301" s="2" t="n">
-        <v>0.11712747</v>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="B302" s="2" t="n">
-        <v>0.11712715</v>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" s="2" t="n">
-        <v>302</v>
-      </c>
-      <c r="B303" s="2" t="n">
-        <v>0.11712684</v>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" s="2" t="n">
-        <v>303</v>
-      </c>
-      <c r="B304" s="2" t="n">
-        <v>0.11712654</v>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" s="2" t="n">
-        <v>304</v>
-      </c>
-      <c r="B305" s="2" t="n">
-        <v>0.11712626</v>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" s="2" t="n">
-        <v>305</v>
-      </c>
-      <c r="B306" s="2" t="n">
-        <v>0.11712598</v>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" s="2" t="n">
-        <v>306</v>
-      </c>
-      <c r="B307" s="2" t="n">
-        <v>0.11712571</v>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" s="2" t="n">
-        <v>307</v>
-      </c>
-      <c r="B308" s="2" t="n">
-        <v>0.11712545</v>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" s="2" t="n">
-        <v>308</v>
-      </c>
-      <c r="B309" s="2" t="n">
-        <v>0.1171252</v>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" s="2" t="n">
-        <v>309</v>
-      </c>
-      <c r="B310" s="2" t="n">
-        <v>0.11712495</v>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" s="2" t="n">
-        <v>310</v>
-      </c>
-      <c r="B311" s="2" t="n">
-        <v>0.11712472</v>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" s="2" t="n">
-        <v>311</v>
-      </c>
-      <c r="B312" s="2" t="n">
-        <v>0.11712449</v>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" s="2" t="n">
-        <v>312</v>
-      </c>
-      <c r="B313" s="2" t="n">
-        <v>0.11712427</v>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" s="2" t="n">
-        <v>313</v>
-      </c>
-      <c r="B314" s="2" t="n">
-        <v>0.11712406</v>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" s="2" t="n">
-        <v>314</v>
-      </c>
-      <c r="B315" s="2" t="n">
-        <v>0.11712386</v>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" s="2" t="n">
-        <v>315</v>
-      </c>
-      <c r="B316" s="2" t="n">
-        <v>0.11712366</v>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" s="2" t="n">
-        <v>316</v>
-      </c>
-      <c r="B317" s="2" t="n">
-        <v>0.11712347</v>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" s="2" t="n">
-        <v>317</v>
-      </c>
-      <c r="B318" s="2" t="n">
-        <v>0.11712328</v>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" s="2" t="n">
-        <v>318</v>
-      </c>
-      <c r="B319" s="2" t="n">
-        <v>0.1171231</v>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" s="2" t="n">
-        <v>319</v>
-      </c>
-      <c r="B320" s="2" t="n">
-        <v>0.11712293</v>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" s="2" t="n">
-        <v>320</v>
-      </c>
-      <c r="B321" s="2" t="n">
-        <v>0.11712276</v>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" s="2" t="n">
-        <v>321</v>
-      </c>
-      <c r="B322" s="2" t="n">
-        <v>0.1171226</v>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" s="2" t="n">
-        <v>322</v>
-      </c>
-      <c r="B323" s="2" t="n">
-        <v>0.11712245</v>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" s="2" t="n">
-        <v>323</v>
-      </c>
-      <c r="B324" s="2" t="n">
-        <v>0.1171223</v>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" s="2" t="n">
-        <v>324</v>
-      </c>
-      <c r="B325" s="2" t="n">
-        <v>0.11712215</v>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" s="2" t="n">
-        <v>325</v>
-      </c>
-      <c r="B326" s="2" t="n">
-        <v>0.11712201</v>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" s="2" t="n">
-        <v>326</v>
-      </c>
-      <c r="B327" s="2" t="n">
-        <v>0.11712187</v>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" s="2" t="n">
-        <v>327</v>
-      </c>
-      <c r="B328" s="2" t="n">
-        <v>0.11712174</v>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" s="2" t="n">
-        <v>328</v>
-      </c>
-      <c r="B329" s="2" t="n">
-        <v>0.11712162</v>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" s="2" t="n">
-        <v>329</v>
-      </c>
-      <c r="B330" s="2" t="n">
-        <v>0.11712149</v>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" s="2" t="n">
-        <v>330</v>
-      </c>
-      <c r="B331" s="2" t="n">
-        <v>0.11712137</v>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" s="2" t="n">
-        <v>331</v>
-      </c>
-      <c r="B332" s="2" t="n">
-        <v>0.11712126</v>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" s="2" t="n">
-        <v>332</v>
-      </c>
-      <c r="B333" s="2" t="n">
-        <v>0.11712115</v>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" s="2" t="n">
-        <v>333</v>
-      </c>
-      <c r="B334" s="2" t="n">
-        <v>0.11712104</v>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" s="2" t="n">
-        <v>334</v>
-      </c>
-      <c r="B335" s="2" t="n">
-        <v>0.11712094</v>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" s="2" t="n">
-        <v>335</v>
-      </c>
-      <c r="B336" s="2" t="n">
-        <v>0.11712084</v>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" s="2" t="n">
-        <v>336</v>
-      </c>
-      <c r="B337" s="2" t="n">
-        <v>0.11712074</v>
+        <v>0.12081422</v>
       </c>
     </row>
   </sheetData>
